--- a/public/downloads/LungerCation-dependent2022.xlsx
+++ b/public/downloads/LungerCation-dependent2022.xlsx
@@ -8,14 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="40">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -47,10 +49,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
-  </si>
-  <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_total (ms)</t>
+  </si>
+  <si>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -604,9 +606,7 @@
       <c r="H3" s="4">
         <v>5.652518371715422</v>
       </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
+      <c r="I3" s="4"/>
       <c r="J3" s="4">
         <v>6.286944043610768</v>
       </c>
@@ -620,10 +620,10 @@
         <v>45</v>
       </c>
       <c r="N3" s="5">
-        <v>303.4045360088348</v>
+        <v>303404.5360088348</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03412490563590539</v>
+        <v>34.12490563590539</v>
       </c>
       <c r="P3" s="5">
         <v>8891</v>
@@ -654,9 +654,7 @@
       <c r="H4" s="4">
         <v>3.946455662754783</v>
       </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
+      <c r="I4" s="4"/>
       <c r="J4" s="4">
         <v>6.120278828648338</v>
       </c>
@@ -670,10 +668,10 @@
         <v>45</v>
       </c>
       <c r="N4" s="5">
-        <v>1430.806243896484</v>
+        <v>1430806.243896484</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06236352019772847</v>
+        <v>62.36352019772847</v>
       </c>
       <c r="P4" s="5">
         <v>22943</v>
@@ -720,10 +718,10 @@
         <v>45</v>
       </c>
       <c r="N5" s="5">
-        <v>1116.422018766403</v>
+        <v>1116422.018766403</v>
       </c>
       <c r="O5" s="4">
-        <v>0.142984377403484</v>
+        <v>142.984377403484</v>
       </c>
       <c r="P5" s="5">
         <v>7808</v>
@@ -770,10 +768,10 @@
         <v>45</v>
       </c>
       <c r="N6" s="5">
-        <v>1427.745730638504</v>
+        <v>1427745.730638504</v>
       </c>
       <c r="O6" s="4">
-        <v>0.0869039948042184</v>
+        <v>86.9039948042184</v>
       </c>
       <c r="P6" s="5">
         <v>16429</v>
@@ -804,9 +802,7 @@
       <c r="H7" s="4">
         <v>9.805955011289262</v>
       </c>
-      <c r="I7" s="4">
-        <v>0</v>
-      </c>
+      <c r="I7" s="4"/>
       <c r="J7" s="4">
         <v>11.98062033518249</v>
       </c>
@@ -820,10 +816,10 @@
         <v>45</v>
       </c>
       <c r="N7" s="5">
-        <v>1615.114879608154</v>
+        <v>1615114.879608154</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2205838404272268</v>
+        <v>220.5838404272268</v>
       </c>
       <c r="P7" s="5">
         <v>7322</v>
@@ -870,10 +866,10 @@
         <v>45</v>
       </c>
       <c r="N8" s="5">
-        <v>123.477109670639</v>
+        <v>123477.109670639</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01738869309542868</v>
+        <v>17.38869309542868</v>
       </c>
       <c r="P8" s="5">
         <v>7101</v>
@@ -904,9 +900,7 @@
       <c r="H9" s="4">
         <v>5.071771371339039</v>
       </c>
-      <c r="I9" s="4">
-        <v>0</v>
-      </c>
+      <c r="I9" s="4"/>
       <c r="J9" s="4">
         <v>7.017286845022714</v>
       </c>
@@ -920,10 +914,10 @@
         <v>45</v>
       </c>
       <c r="N9" s="5">
-        <v>477.5829977989197</v>
+        <v>477582.9977989197</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03375383403766483</v>
+        <v>33.75383403766483</v>
       </c>
       <c r="P9" s="5">
         <v>14149</v>
@@ -970,10 +964,10 @@
         <v>45</v>
       </c>
       <c r="N10" s="5">
-        <v>866.1579036712646</v>
+        <v>866157.9036712646</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08414201512252426</v>
+        <v>84.14201512252426</v>
       </c>
       <c r="P10" s="5">
         <v>10294</v>
@@ -1020,10 +1014,10 @@
         <v>45</v>
       </c>
       <c r="N11" s="5">
-        <v>347.5846509933472</v>
+        <v>347584.6509933472</v>
       </c>
       <c r="O11" s="4">
-        <v>0.0420041874312202</v>
+        <v>42.0041874312202</v>
       </c>
       <c r="P11" s="5">
         <v>8275</v>
@@ -1054,9 +1048,7 @@
       <c r="H12" s="4">
         <v>3.935599776083505</v>
       </c>
-      <c r="I12" s="4">
-        <v>0</v>
-      </c>
+      <c r="I12" s="4"/>
       <c r="J12" s="4">
         <v>6.227039553033918</v>
       </c>
@@ -1070,10 +1062,10 @@
         <v>45</v>
       </c>
       <c r="N12" s="5">
-        <v>168.5828227996826</v>
+        <v>168582.8227996826</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02108866935197431</v>
+        <v>21.08866935197431</v>
       </c>
       <c r="P12" s="5">
         <v>7994</v>
@@ -1104,9 +1096,7 @@
       <c r="H13" s="4">
         <v>4.664493389898812</v>
       </c>
-      <c r="I13" s="4">
-        <v>0</v>
-      </c>
+      <c r="I13" s="4"/>
       <c r="J13" s="4">
         <v>6.590576647362056</v>
       </c>
@@ -1120,10 +1110,10 @@
         <v>45</v>
       </c>
       <c r="N13" s="5">
-        <v>777.9933757781982</v>
+        <v>777993.3757781982</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07641620428034557</v>
+        <v>76.41620428034557</v>
       </c>
       <c r="P13" s="5">
         <v>10181</v>
@@ -1151,6 +1141,659 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>40</v>
+      </c>
+      <c r="G3" s="3">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="H3" s="4">
+        <v>4.857850290202455</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3180189213151105</v>
+      </c>
+      <c r="J3" s="4">
+        <v>5.368188685703703</v>
+      </c>
+      <c r="K3" s="4">
+        <v>72.97883597883585</v>
+      </c>
+      <c r="L3" s="4">
+        <v>68.89386030325733</v>
+      </c>
+      <c r="M3" s="5">
+        <v>45</v>
+      </c>
+      <c r="N3" s="5">
+        <v>303404.5360088348</v>
+      </c>
+      <c r="O3" s="4">
+        <v>34.12490563590539</v>
+      </c>
+      <c r="P3" s="5">
+        <v>8891</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3">
+        <v>31.11111111111111</v>
+      </c>
+      <c r="F4" s="3">
+        <v>28.88888888888889</v>
+      </c>
+      <c r="G4" s="3">
+        <v>40</v>
+      </c>
+      <c r="H4" s="4">
+        <v>3.946455662754783</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4">
+        <v>6.120278828648338</v>
+      </c>
+      <c r="K4" s="4">
+        <v>47.27059712774021</v>
+      </c>
+      <c r="L4" s="4">
+        <v>49.78846631866763</v>
+      </c>
+      <c r="M4" s="5">
+        <v>45</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1430806.243896484</v>
+      </c>
+      <c r="O4" s="4">
+        <v>62.36352019772847</v>
+      </c>
+      <c r="P4" s="5">
+        <v>22943</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="D5" s="3">
+        <v>77.77777777777779</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>31.11111111111111</v>
+      </c>
+      <c r="G5" s="3">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="H5" s="4">
+        <v>7.632657070452155</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1.500464010769507</v>
+      </c>
+      <c r="J5" s="4">
+        <v>6.791953367672646</v>
+      </c>
+      <c r="K5" s="4">
+        <v>68.72108843537401</v>
+      </c>
+      <c r="L5" s="4">
+        <v>71.89758886403278</v>
+      </c>
+      <c r="M5" s="5">
+        <v>45</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1116422.018766403</v>
+      </c>
+      <c r="O5" s="4">
+        <v>142.984377403484</v>
+      </c>
+      <c r="P5" s="5">
+        <v>7808</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="C6" s="3">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="D6" s="3">
+        <v>80</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="G6" s="3">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="H6" s="4">
+        <v>4.430195764675017</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1.603972170178755</v>
+      </c>
+      <c r="J6" s="4">
+        <v>5.737167113331566</v>
+      </c>
+      <c r="K6" s="4">
+        <v>76.5479969765685</v>
+      </c>
+      <c r="L6" s="4">
+        <v>71.16032811334775</v>
+      </c>
+      <c r="M6" s="5">
+        <v>45</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1427745.730638504</v>
+      </c>
+      <c r="O6" s="4">
+        <v>86.9039948042184</v>
+      </c>
+      <c r="P6" s="5">
+        <v>16429</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G7" s="3">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="H7" s="4">
+        <v>4.447480678208414</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.4080766507291561</v>
+      </c>
+      <c r="J7" s="4">
+        <v>6.404505121712759</v>
+      </c>
+      <c r="K7" s="4">
+        <v>85.07029478458037</v>
+      </c>
+      <c r="L7" s="4">
+        <v>81.49241859309022</v>
+      </c>
+      <c r="M7" s="5">
+        <v>45</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1615114.879608154</v>
+      </c>
+      <c r="O7" s="4">
+        <v>220.5838404272268</v>
+      </c>
+      <c r="P7" s="5">
+        <v>7322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>60</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>40</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>20</v>
+      </c>
+      <c r="G8" s="3">
+        <v>20</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1.097746744142124</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.6068770409432789</v>
+      </c>
+      <c r="J8" s="4">
+        <v>3.053557241153962</v>
+      </c>
+      <c r="K8" s="4">
+        <v>83.10204081632662</v>
+      </c>
+      <c r="L8" s="4">
+        <v>81.07382550335721</v>
+      </c>
+      <c r="M8" s="5">
+        <v>45</v>
+      </c>
+      <c r="N8" s="5">
+        <v>123477.109670639</v>
+      </c>
+      <c r="O8" s="4">
+        <v>17.38869309542868</v>
+      </c>
+      <c r="P8" s="5">
+        <v>7101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>60</v>
+      </c>
+      <c r="G9" s="3">
+        <v>40</v>
+      </c>
+      <c r="H9" s="4">
+        <v>5.071771371339039</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4">
+        <v>7.017286845022714</v>
+      </c>
+      <c r="K9" s="4">
+        <v>62.90249433106544</v>
+      </c>
+      <c r="L9" s="4">
+        <v>58.87422321650622</v>
+      </c>
+      <c r="M9" s="5">
+        <v>45</v>
+      </c>
+      <c r="N9" s="5">
+        <v>477582.9977989197</v>
+      </c>
+      <c r="O9" s="4">
+        <v>33.75383403766483</v>
+      </c>
+      <c r="P9" s="5">
+        <v>14149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>53.33333333333334</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>40</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="H10" s="4">
+        <v>1.370700415459039</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.6161100773622452</v>
+      </c>
+      <c r="J10" s="4">
+        <v>6.680810797308957</v>
+      </c>
+      <c r="K10" s="4">
+        <v>82.04535147392285</v>
+      </c>
+      <c r="L10" s="4">
+        <v>80.31245339299181</v>
+      </c>
+      <c r="M10" s="5">
+        <v>45</v>
+      </c>
+      <c r="N10" s="5">
+        <v>866157.9036712646</v>
+      </c>
+      <c r="O10" s="4">
+        <v>84.14201512252426</v>
+      </c>
+      <c r="P10" s="5">
+        <v>10294</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="G11" s="3">
+        <v>20</v>
+      </c>
+      <c r="H11" s="4">
+        <v>4.654966083465447</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.6529940300947829</v>
+      </c>
+      <c r="J11" s="4">
+        <v>5.262899413584238</v>
+      </c>
+      <c r="K11" s="4">
+        <v>75.64777021919906</v>
+      </c>
+      <c r="L11" s="4">
+        <v>74.32115336813483</v>
+      </c>
+      <c r="M11" s="5">
+        <v>45</v>
+      </c>
+      <c r="N11" s="5">
+        <v>347584.6509933472</v>
+      </c>
+      <c r="O11" s="4">
+        <v>42.0041874312202</v>
+      </c>
+      <c r="P11" s="5">
+        <v>8275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="G12" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="H12" s="4">
+        <v>2.382492603004121</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1367584383756461</v>
+      </c>
+      <c r="J12" s="4">
+        <v>4.13854160924274</v>
+      </c>
+      <c r="K12" s="4">
+        <v>80.23129251700682</v>
+      </c>
+      <c r="L12" s="4">
+        <v>74.60526969923085</v>
+      </c>
+      <c r="M12" s="5">
+        <v>45</v>
+      </c>
+      <c r="N12" s="5">
+        <v>168582.8227996826</v>
+      </c>
+      <c r="O12" s="4">
+        <v>21.08866935197431</v>
+      </c>
+      <c r="P12" s="5">
+        <v>7994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>40</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>60</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>60</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1.873066744274161</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.4063350247157003</v>
+      </c>
+      <c r="J13" s="4">
+        <v>3.636615991851124</v>
+      </c>
+      <c r="K13" s="4">
+        <v>71.08012093726359</v>
+      </c>
+      <c r="L13" s="4">
+        <v>59.84389758886402</v>
+      </c>
+      <c r="M13" s="5">
+        <v>45</v>
+      </c>
+      <c r="N13" s="5">
+        <v>777993.3757781982</v>
+      </c>
+      <c r="O13" s="4">
+        <v>76.41620428034557</v>
+      </c>
+      <c r="P13" s="5">
+        <v>10181</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1307,16 +1950,16 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -1692,6 +2335,585 @@
       </c>
       <c r="G13" s="5">
         <v>18</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>9</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>39</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5">
+        <v>21</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>12</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>45</v>
+      </c>
+      <c r="E4" s="5">
+        <v>14</v>
+      </c>
+      <c r="F4" s="5">
+        <v>13</v>
+      </c>
+      <c r="G4" s="5">
+        <v>18</v>
+      </c>
+      <c r="H4" s="5">
+        <v>14</v>
+      </c>
+      <c r="I4" s="5">
+        <v>5</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>10</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>35</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>14</v>
+      </c>
+      <c r="G5" s="5">
+        <v>21</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>14</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5">
+        <v>6</v>
+      </c>
+      <c r="D6" s="5">
+        <v>36</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5">
+        <v>24</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>3</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>21</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>15</v>
+      </c>
+      <c r="G7" s="5">
+        <v>6</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>6</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>27</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>18</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>9</v>
+      </c>
+      <c r="G8" s="5">
+        <v>9</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>9</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>45</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>27</v>
+      </c>
+      <c r="G9" s="5">
+        <v>18</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>15</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>24</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>21</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>18</v>
+      </c>
+      <c r="G10" s="5">
+        <v>3</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>9</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>15</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>30</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>21</v>
+      </c>
+      <c r="G11" s="5">
+        <v>9</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>9</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>33</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>21</v>
+      </c>
+      <c r="G12" s="5">
+        <v>12</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>6</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>18</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>27</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>27</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
       </c>
       <c r="H13" s="5">
         <v>0</v>

--- a/public/downloads/LungerCation-dependent2022.xlsx
+++ b/public/downloads/LungerCation-dependent2022.xlsx
@@ -1249,13 +1249,13 @@
         <v>46.66666666666666</v>
       </c>
       <c r="H3" s="4">
-        <v>4.857850290202455</v>
+        <v>4.857818077203323</v>
       </c>
       <c r="I3" s="4">
         <v>0.3180189213151105</v>
       </c>
       <c r="J3" s="4">
-        <v>5.368188685703703</v>
+        <v>5.368285324701098</v>
       </c>
       <c r="K3" s="4">
         <v>72.97883597883585</v>
@@ -1347,13 +1347,13 @@
         <v>46.66666666666666</v>
       </c>
       <c r="H5" s="4">
-        <v>7.632657070452155</v>
+        <v>7.632657066975217</v>
       </c>
       <c r="I5" s="4">
         <v>1.500464010769507</v>
       </c>
       <c r="J5" s="4">
-        <v>6.791953367672646</v>
+        <v>6.791953357241833</v>
       </c>
       <c r="K5" s="4">
         <v>68.72108843537401</v>
@@ -1447,13 +1447,13 @@
         <v>13.33333333333333</v>
       </c>
       <c r="H7" s="4">
-        <v>4.447480678208414</v>
+        <v>4.411954443213623</v>
       </c>
       <c r="I7" s="4">
-        <v>0.4080766507291561</v>
+        <v>0.341465595896801</v>
       </c>
       <c r="J7" s="4">
-        <v>6.404505121712759</v>
+        <v>6.297926416728387</v>
       </c>
       <c r="K7" s="4">
         <v>85.07029478458037</v>
@@ -1497,13 +1497,13 @@
         <v>20</v>
       </c>
       <c r="H8" s="4">
-        <v>1.097746744142124</v>
+        <v>1.069069718995066</v>
       </c>
       <c r="I8" s="4">
-        <v>0.6068770409432789</v>
+        <v>0.5590819990315155</v>
       </c>
       <c r="J8" s="4">
-        <v>3.053557241153962</v>
+        <v>3.139588316595136</v>
       </c>
       <c r="K8" s="4">
         <v>83.10204081632662</v>
@@ -1595,13 +1595,13 @@
         <v>6.666666666666667</v>
       </c>
       <c r="H10" s="4">
-        <v>1.370700415459039</v>
+        <v>1.34719237456511</v>
       </c>
       <c r="I10" s="4">
-        <v>0.6161100773622452</v>
+        <v>0.572032216751645</v>
       </c>
       <c r="J10" s="4">
-        <v>6.680810797308957</v>
+        <v>6.751336354301692</v>
       </c>
       <c r="K10" s="4">
         <v>82.04535147392285</v>
@@ -1645,13 +1645,13 @@
         <v>20</v>
       </c>
       <c r="H11" s="4">
-        <v>4.654966083465447</v>
+        <v>4.654965405297044</v>
       </c>
       <c r="I11" s="4">
         <v>0.6529940300947829</v>
       </c>
       <c r="J11" s="4">
-        <v>5.262899413584238</v>
+        <v>5.262901448089447</v>
       </c>
       <c r="K11" s="4">
         <v>75.64777021919906</v>
@@ -1695,13 +1695,13 @@
         <v>26.66666666666667</v>
       </c>
       <c r="H12" s="4">
-        <v>2.382492603004121</v>
+        <v>2.382558893965493</v>
       </c>
       <c r="I12" s="4">
         <v>0.1367584383756461</v>
       </c>
       <c r="J12" s="4">
-        <v>4.13854160924274</v>
+        <v>4.138342736358624</v>
       </c>
       <c r="K12" s="4">
         <v>80.23129251700682</v>
